--- a/uploads/govt_plot_excels/Govt_Land_Plot.xlsx
+++ b/uploads/govt_plot_excels/Govt_Land_Plot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7273F14-4F96-472C-83CD-4FA2EBBFC21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BDFC14-BB41-4319-9666-49015D96E35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Summary of column codes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plot!$B$2:$AF$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plot!$B$3:$AF$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,10 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
-  <si>
-    <t>MOUZA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="99">
   <si>
     <t>Tahasil</t>
   </si>
@@ -79,9 +76,6 @@
     <t>Present Status</t>
   </si>
   <si>
-    <t>UA /IDCO to Tahasildar</t>
-  </si>
-  <si>
     <t>Action to be taken</t>
   </si>
   <si>
@@ -100,24 +94,15 @@
     <t>Modification/Revision</t>
   </si>
   <si>
-    <t>Mising Case Prep./ DR Case. Prep.</t>
-  </si>
-  <si>
     <t>Reason for Misc/DR case</t>
   </si>
   <si>
     <t>Tree Enumeration</t>
   </si>
   <si>
-    <t>Order Sheet Prep.</t>
-  </si>
-  <si>
     <t>Lease to IDCO</t>
   </si>
   <si>
-    <t>Lease to  UA</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -160,9 +145,6 @@
     <t>lack of proper notice</t>
   </si>
   <si>
-    <t>case details/de-reservation req.</t>
-  </si>
-  <si>
     <t>Missing Case Prep./DR Case Number</t>
   </si>
   <si>
@@ -304,7 +286,52 @@
     <t>CR05</t>
   </si>
   <si>
-    <t>SL NO</t>
+    <t>Handigoda</t>
+  </si>
+  <si>
+    <t>Nalla</t>
+  </si>
+  <si>
+    <t>A A A</t>
+  </si>
+  <si>
+    <t>113/2007</t>
+  </si>
+  <si>
+    <t>Lease case to ADM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes </t>
+  </si>
+  <si>
+    <t>to settle land with individuals who have long term possession (unauthorized)</t>
+  </si>
+  <si>
+    <t>Diversion of private gain (it stated for public purpose but transferred to private company)</t>
+  </si>
+  <si>
+    <t>Machakuta</t>
+  </si>
+  <si>
+    <t>Rasta</t>
+  </si>
+  <si>
+    <t>Sarbasadharan</t>
+  </si>
+  <si>
+    <t>49/2001</t>
+  </si>
+  <si>
+    <t>Demand raised</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Rectifying errors in the records of right that arise during land management.</t>
+  </si>
+  <si>
+    <t>excessive land acquisition (the area acquired is far in excess of the actual requirement for proposed project.</t>
   </si>
 </sst>
 </file>
@@ -314,7 +341,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,35 +350,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,14 +365,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -376,14 +375,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -406,61 +399,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -472,24 +418,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -498,6 +450,8 @@
   <dxfs count="2">
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -508,8 +462,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -818,14 +770,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="5" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="12" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" customWidth="1"/>
     <col min="15" max="15" width="20.5703125" customWidth="1"/>
@@ -842,304 +794,486 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="I1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="J1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="K1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="L1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="M1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="N1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="O1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="P1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="Q1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="R1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="S1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="T1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="U1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="V1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="W1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="X1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="AC1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="AD1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="AE1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="AF1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="W1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="X1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:32" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="S2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Z2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC2" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AD2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE2" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AB1" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC1" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD1" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE1" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="AF2" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="E3" s="2">
+        <v>75</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="G3" s="2">
+        <v>1006</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AF2" s="8" t="s">
+      <c r="I3" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" ht="105" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="9">
-        <v>75</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="9">
-        <v>1006</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="9">
+      <c r="J3" s="2">
         <v>1378</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="6">
         <f>M3/2.471</f>
         <v>0.1800890327802509</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="6">
         <f>N3/2.471</f>
         <v>0.17814649939295829</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="6">
         <v>0.44500000000000001</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="6">
         <v>0.44019999999999998</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="T3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>123</v>
+      </c>
+      <c r="AA3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="S3" s="11" t="s">
+    </row>
+    <row r="4" spans="1:32" ht="120" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="9">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF3" s="9" t="s">
+      <c r="C4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2">
+        <v>76</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="2">
+        <v>410</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="2">
+        <v>26</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" ref="K4:L5" si="0">M4/2.471</f>
+        <v>2.5698097936058276E-2</v>
+      </c>
+      <c r="L4" s="6">
+        <f t="shared" si="0"/>
+        <v>2.4888709024686359E-2</v>
+      </c>
+      <c r="M4" s="6">
+        <v>6.3500000000000001E-2</v>
+      </c>
+      <c r="N4" s="6">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="120" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2">
         <v>40</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="12">
+        <v>416</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="14">
+        <v>2449</v>
+      </c>
+      <c r="K5" s="6">
+        <f t="shared" si="0"/>
+        <v>6.0704168352893564E-2</v>
+      </c>
+      <c r="L5" s="6">
+        <f t="shared" si="0"/>
+        <v>6.0704168352893564E-2</v>
+      </c>
+      <c r="M5" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="N5" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="J2 J4:J1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="J3">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="J6:J1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1156,359 +1290,359 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="B6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B9" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="C9" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="B10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="B11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="B12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="B14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="B15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="B16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="B17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="B18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="B19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="B20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="B21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="B22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="B23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="B28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="B29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="B30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="B31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="15" t="s">
+      <c r="B32" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="15" t="s">
+      <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/uploads/govt_plot_excels/Govt_Land_Plot.xlsx
+++ b/uploads/govt_plot_excels/Govt_Land_Plot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7273F14-4F96-472C-83CD-4FA2EBBFC21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D31321-D1B8-4650-BEF9-E6053A1E9455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Summary of column codes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plot!$B$2:$AF$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plot!$B$3:$AF$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,10 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
-  <si>
-    <t>MOUZA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
   <si>
     <t>Tahasil</t>
   </si>
@@ -79,9 +76,6 @@
     <t>Present Status</t>
   </si>
   <si>
-    <t>UA /IDCO to Tahasildar</t>
-  </si>
-  <si>
     <t>Action to be taken</t>
   </si>
   <si>
@@ -100,24 +94,15 @@
     <t>Modification/Revision</t>
   </si>
   <si>
-    <t>Mising Case Prep./ DR Case. Prep.</t>
-  </si>
-  <si>
     <t>Reason for Misc/DR case</t>
   </si>
   <si>
     <t>Tree Enumeration</t>
   </si>
   <si>
-    <t>Order Sheet Prep.</t>
-  </si>
-  <si>
     <t>Lease to IDCO</t>
   </si>
   <si>
-    <t>Lease to  UA</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -160,9 +145,6 @@
     <t>lack of proper notice</t>
   </si>
   <si>
-    <t>case details/de-reservation req.</t>
-  </si>
-  <si>
     <t>Missing Case Prep./DR Case Number</t>
   </si>
   <si>
@@ -302,9 +284,6 @@
   </si>
   <si>
     <t>CR05</t>
-  </si>
-  <si>
-    <t>SL NO</t>
   </si>
 </sst>
 </file>
@@ -314,7 +293,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,35 +302,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,30 +317,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -406,61 +345,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -472,19 +364,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -498,6 +387,8 @@
   <dxfs count="2">
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -508,8 +399,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -823,9 +712,9 @@
   <cols>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="5" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="12" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" customWidth="1"/>
     <col min="15" max="15" width="20.5703125" customWidth="1"/>
@@ -842,304 +731,302 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="I1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="J1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="K1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="L1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="M1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="N1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="O1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="P1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="Q1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="R1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="S1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="T1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="U1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="V1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="W1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="X1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="AC1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="AD1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="AE1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="AF1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="W1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="X1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:32" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="S2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Z2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC2" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AD2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE2" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AB1" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC1" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD1" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE1" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="AF2" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="E3" s="2">
+        <v>75</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="G3" s="2">
+        <v>1006</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AF2" s="8" t="s">
+      <c r="I3" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" ht="105" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="9">
-        <v>75</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="9">
-        <v>1006</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="9">
+      <c r="J3" s="2">
         <v>1378</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="6">
         <f>M3/2.471</f>
         <v>0.1800890327802509</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="6">
         <f>N3/2.471</f>
         <v>0.17814649939295829</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="6">
         <v>0.44500000000000001</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="6">
         <v>0.44019999999999998</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="T3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>123</v>
+      </c>
+      <c r="AA3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="9">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF3" s="9" t="s">
-        <v>40</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="J2 J4:J1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="J3">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="J4:J1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1156,359 +1043,359 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="B6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B9" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="C9" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="B10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="B11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="B12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="B14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="B15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="B16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="B17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="B18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="B19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="B20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="B21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="B22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="B23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="B28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="B29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="B30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="B31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="15" t="s">
+      <c r="B32" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="15" t="s">
+      <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/uploads/govt_plot_excels/Govt_Land_Plot.xlsx
+++ b/uploads/govt_plot_excels/Govt_Land_Plot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D31321-D1B8-4650-BEF9-E6053A1E9455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BDFC14-BB41-4319-9666-49015D96E35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="99">
   <si>
     <t>Tahasil</t>
   </si>
@@ -284,6 +284,54 @@
   </si>
   <si>
     <t>CR05</t>
+  </si>
+  <si>
+    <t>Handigoda</t>
+  </si>
+  <si>
+    <t>Nalla</t>
+  </si>
+  <si>
+    <t>A A A</t>
+  </si>
+  <si>
+    <t>113/2007</t>
+  </si>
+  <si>
+    <t>Lease case to ADM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes </t>
+  </si>
+  <si>
+    <t>to settle land with individuals who have long term possession (unauthorized)</t>
+  </si>
+  <si>
+    <t>Diversion of private gain (it stated for public purpose but transferred to private company)</t>
+  </si>
+  <si>
+    <t>Machakuta</t>
+  </si>
+  <si>
+    <t>Rasta</t>
+  </si>
+  <si>
+    <t>Sarbasadharan</t>
+  </si>
+  <si>
+    <t>49/2001</t>
+  </si>
+  <si>
+    <t>Demand raised</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Rectifying errors in the records of right that arise during land management.</t>
+  </si>
+  <si>
+    <t>excessive land acquisition (the area acquired is far in excess of the actual requirement for proposed project.</t>
   </si>
 </sst>
 </file>
@@ -308,7 +356,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,6 +366,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -349,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -379,6 +433,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -707,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
@@ -1020,12 +1083,196 @@
         <v>35</v>
       </c>
     </row>
+    <row r="4" spans="1:32" ht="120" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2">
+        <v>76</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="2">
+        <v>410</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="2">
+        <v>26</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" ref="K4:L5" si="0">M4/2.471</f>
+        <v>2.5698097936058276E-2</v>
+      </c>
+      <c r="L4" s="6">
+        <f t="shared" si="0"/>
+        <v>2.4888709024686359E-2</v>
+      </c>
+      <c r="M4" s="6">
+        <v>6.3500000000000001E-2</v>
+      </c>
+      <c r="N4" s="6">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="120" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2">
+        <v>40</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="12">
+        <v>416</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="14">
+        <v>2449</v>
+      </c>
+      <c r="K5" s="6">
+        <f t="shared" si="0"/>
+        <v>6.0704168352893564E-2</v>
+      </c>
+      <c r="L5" s="6">
+        <f t="shared" si="0"/>
+        <v>6.0704168352893564E-2</v>
+      </c>
+      <c r="M5" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="N5" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="J3">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J1048576">
+  <conditionalFormatting sqref="J6:J1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
